--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4143,6 +4143,569 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131926796</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>514063</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6583964</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131926927</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>514025</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6584048</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131926958</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58447</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>514036</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6584061</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131926865</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>514074</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6583986</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131926981</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>514036</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6584061</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4706,6 +4706,125 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131946206</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>O Ölmbrotorp, Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>514027</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6584093</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Per Wedholm</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Per Wedholm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -4372,7 +4372,7 @@
         <v>131926958</v>
       </c>
       <c r="B32" t="n">
-        <v>58490</v>
+        <v>58492</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -4148,7 +4148,7 @@
         <v>131926796</v>
       </c>
       <c r="B30" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>131926927</v>
       </c>
       <c r="B31" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>131926958</v>
       </c>
       <c r="B32" t="n">
-        <v>58492</v>
+        <v>58493</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>131926865</v>
       </c>
       <c r="B33" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>131926981</v>
       </c>
       <c r="B34" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>131946206</v>
       </c>
       <c r="B35" t="n">
-        <v>57942</v>
+        <v>57943</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -4148,7 +4148,7 @@
         <v>131926796</v>
       </c>
       <c r="B30" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>131926927</v>
       </c>
       <c r="B31" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>131926958</v>
       </c>
       <c r="B32" t="n">
-        <v>58493</v>
+        <v>58497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>131926865</v>
       </c>
       <c r="B33" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>131926981</v>
       </c>
       <c r="B34" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>131946206</v>
       </c>
       <c r="B35" t="n">
-        <v>57943</v>
+        <v>57947</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>124893048</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>124893054</v>
       </c>
       <c r="B3" t="n">
-        <v>91186</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>124893218</v>
       </c>
       <c r="B4" t="n">
-        <v>90736</v>
+        <v>91282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893139</v>
+        <v>124893056</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,46 +1047,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514210</v>
+        <v>514185</v>
       </c>
       <c r="R5" t="n">
-        <v>6583882</v>
+        <v>6584037</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,24 +1120,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1158,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124893046</v>
+        <v>131926796</v>
       </c>
       <c r="B6" t="n">
-        <v>5196</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1189,19 +1169,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514014</v>
+        <v>514063</v>
       </c>
       <c r="R6" t="n">
-        <v>6584124</v>
+        <v>6583964</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,12 +1208,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,45 +1234,30 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124893056</v>
+        <v>131926865</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1306,19 +1281,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514185</v>
+        <v>514074</v>
       </c>
       <c r="R7" t="n">
-        <v>6584037</v>
+        <v>6583986</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,12 +1320,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124893050</v>
+        <v>131926927</v>
       </c>
       <c r="B8" t="n">
-        <v>5196</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,16 +1373,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1408,19 +1393,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514010</v>
+        <v>514025</v>
       </c>
       <c r="R8" t="n">
-        <v>6583953</v>
+        <v>6584048</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,12 +1432,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,98 +1458,69 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128848287</v>
+        <v>131926981</v>
       </c>
       <c r="B9" t="n">
-        <v>56593</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514153</v>
+        <v>514036</v>
       </c>
       <c r="R9" t="n">
-        <v>6583896</v>
+        <v>6584061</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,22 +1544,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,49 +1574,49 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128848250</v>
+        <v>128848252</v>
       </c>
       <c r="B10" t="n">
-        <v>56593</v>
+        <v>56830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1746,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128848252</v>
+        <v>128848267</v>
       </c>
       <c r="B11" t="n">
-        <v>56607</v>
+        <v>56830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1742,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1791,7 +1757,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ultraljudsdetektor</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1800,13 +1766,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514136</v>
+        <v>514046</v>
       </c>
       <c r="R11" t="n">
-        <v>6583960</v>
+        <v>6583983</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1830,7 +1796,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1845,7 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128848257</v>
+        <v>128848282</v>
       </c>
       <c r="B12" t="n">
-        <v>56600</v>
+        <v>56830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,26 +1849,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1917,7 +1883,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ultraljudsdetektor</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1926,13 +1892,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514136</v>
+        <v>514158</v>
       </c>
       <c r="R12" t="n">
-        <v>6583960</v>
+        <v>6583896</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1956,7 +1922,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1971,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1998,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128848285</v>
+        <v>128848289</v>
       </c>
       <c r="B13" t="n">
-        <v>56600</v>
+        <v>56830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,26 +1975,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2052,7 +2018,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514155</v>
+        <v>514151</v>
       </c>
       <c r="R13" t="n">
         <v>6583896</v>
@@ -2082,17 +2048,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2124,37 +2090,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128848272</v>
+        <v>128848276</v>
       </c>
       <c r="B14" t="n">
-        <v>56593</v>
+        <v>56833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2250,10 +2216,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128848274</v>
+        <v>131946206</v>
       </c>
       <c r="B15" t="n">
-        <v>56607</v>
+        <v>57969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,56 +2227,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Nrk</t>
+          <t>O Ölmbrotorp, Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514046</v>
+        <v>514027</v>
       </c>
       <c r="R15" t="n">
-        <v>6583983</v>
+        <v>6584093</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2334,22 +2293,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,76 +2323,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Per Wedholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Per Wedholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128848282</v>
+        <v>131926958</v>
       </c>
       <c r="B16" t="n">
-        <v>56607</v>
+        <v>58519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100092</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514158</v>
+        <v>514036</v>
       </c>
       <c r="R16" t="n">
-        <v>6583896</v>
+        <v>6584061</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2460,22 +2408,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,22 +2438,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128848276</v>
+        <v>131843000</v>
       </c>
       <c r="B17" t="n">
-        <v>56610</v>
+        <v>58131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,53 +2461,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100111</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514046</v>
+        <v>514180</v>
       </c>
       <c r="R17" t="n">
-        <v>6583983</v>
+        <v>6583942</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2586,22 +2524,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2616,22 +2554,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Per Wedholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Per Wedholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128848270</v>
+        <v>124893046</v>
       </c>
       <c r="B18" t="n">
-        <v>56600</v>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,41 +2577,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2682,13 +2606,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514046</v>
+        <v>514014</v>
       </c>
       <c r="R18" t="n">
-        <v>6583983</v>
+        <v>6584124</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2712,22 +2636,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2738,26 +2652,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128848290</v>
+        <v>124893050</v>
       </c>
       <c r="B19" t="n">
-        <v>56612</v>
+        <v>5199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,41 +2694,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2808,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514151</v>
+        <v>514010</v>
       </c>
       <c r="R19" t="n">
-        <v>6583896</v>
+        <v>6583953</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2838,22 +2753,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2864,26 +2769,41 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128848254</v>
+        <v>124893139</v>
       </c>
       <c r="B20" t="n">
-        <v>56612</v>
+        <v>8444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2891,56 +2811,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514136</v>
+        <v>514210</v>
       </c>
       <c r="R20" t="n">
-        <v>6583960</v>
+        <v>6583882</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2964,22 +2874,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>01:15</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2988,55 +2888,71 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128848280</v>
+        <v>128848257</v>
       </c>
       <c r="B21" t="n">
-        <v>56614</v>
+        <v>56823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3051,7 +2967,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3060,13 +2976,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514160</v>
+        <v>514136</v>
       </c>
       <c r="R21" t="n">
-        <v>6583896</v>
+        <v>6583960</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3090,7 +3006,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3105,7 +3021,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3132,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128848268</v>
+        <v>128848270</v>
       </c>
       <c r="B22" t="n">
-        <v>56612</v>
+        <v>56823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,26 +3059,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3258,10 +3174,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128848292</v>
+        <v>128848285</v>
       </c>
       <c r="B23" t="n">
-        <v>56600</v>
+        <v>56823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3288,7 +3204,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3312,7 +3228,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514148</v>
+        <v>514155</v>
       </c>
       <c r="R23" t="n">
         <v>6583896</v>
@@ -3342,17 +3258,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3384,37 +3300,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128848281</v>
+        <v>128848292</v>
       </c>
       <c r="B24" t="n">
-        <v>56593</v>
+        <v>56823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3438,7 +3354,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514159</v>
+        <v>514148</v>
       </c>
       <c r="R24" t="n">
         <v>6583896</v>
@@ -3468,17 +3384,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3510,10 +3426,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128848283</v>
+        <v>128848254</v>
       </c>
       <c r="B25" t="n">
-        <v>56612</v>
+        <v>56835</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3540,7 +3456,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3555,7 +3471,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3564,13 +3480,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514157</v>
+        <v>514136</v>
       </c>
       <c r="R25" t="n">
-        <v>6583896</v>
+        <v>6583960</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3594,7 +3510,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3609,7 +3525,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3636,37 +3552,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128848259</v>
+        <v>128848268</v>
       </c>
       <c r="B26" t="n">
-        <v>56614</v>
+        <v>56835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3681,7 +3597,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ultraljudsdetektor</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3690,13 +3606,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514136</v>
+        <v>514046</v>
       </c>
       <c r="R26" t="n">
-        <v>6583960</v>
+        <v>6583983</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3720,22 +3636,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3762,10 +3678,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128848289</v>
+        <v>128848283</v>
       </c>
       <c r="B27" t="n">
-        <v>56607</v>
+        <v>56835</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3773,26 +3689,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3816,7 +3732,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514151</v>
+        <v>514157</v>
       </c>
       <c r="R27" t="n">
         <v>6583896</v>
@@ -3846,17 +3762,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3888,32 +3804,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128848286</v>
+        <v>128848290</v>
       </c>
       <c r="B28" t="n">
-        <v>56614</v>
+        <v>56835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3942,7 +3858,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514154</v>
+        <v>514151</v>
       </c>
       <c r="R28" t="n">
         <v>6583896</v>
@@ -4014,37 +3930,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128848264</v>
+        <v>128848250</v>
       </c>
       <c r="B29" t="n">
-        <v>56620</v>
+        <v>56816</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206000</v>
+        <v>205998</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4054,12 +3970,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4068,13 +3984,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514046</v>
+        <v>514136</v>
       </c>
       <c r="R29" t="n">
-        <v>6583983</v>
+        <v>6583960</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4098,7 +4014,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4113,12 +4029,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Sociala ljud/spelsång</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4145,10 +4056,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131926796</v>
+        <v>128848265</v>
       </c>
       <c r="B30" t="n">
-        <v>57950</v>
+        <v>56816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4156,42 +4067,56 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>205998</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514063</v>
+        <v>514046</v>
       </c>
       <c r="R30" t="n">
-        <v>6583964</v>
+        <v>6583983</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4215,22 +4140,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4245,22 +4170,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131926927</v>
+        <v>128848281</v>
       </c>
       <c r="B31" t="n">
-        <v>57950</v>
+        <v>56816</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4268,42 +4193,56 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>205998</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514025</v>
+        <v>514159</v>
       </c>
       <c r="R31" t="n">
-        <v>6584048</v>
+        <v>6583896</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4327,22 +4266,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4357,65 +4296,76 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131926958</v>
+        <v>128848287</v>
       </c>
       <c r="B32" t="n">
-        <v>58497</v>
+        <v>56816</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514036</v>
+        <v>514153</v>
       </c>
       <c r="R32" t="n">
-        <v>6584061</v>
+        <v>6583896</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,22 +4392,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4472,65 +4422,79 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131926865</v>
+        <v>128848264</v>
       </c>
       <c r="B33" t="n">
-        <v>57950</v>
+        <v>56840</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>206000</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråskimlig fladdermus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Vespertilio murinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514074</v>
+        <v>514046</v>
       </c>
       <c r="R33" t="n">
-        <v>6583986</v>
+        <v>6583983</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4554,22 +4518,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sociala ljud/spelsång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4584,22 +4553,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131926981</v>
+        <v>128848259</v>
       </c>
       <c r="B34" t="n">
-        <v>57950</v>
+        <v>56837</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4607,16 +4576,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>206002</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4624,22 +4593,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514036</v>
+        <v>514136</v>
       </c>
       <c r="R34" t="n">
-        <v>6584061</v>
+        <v>6583960</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4666,22 +4649,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4696,44 +4679,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131946206</v>
+        <v>128848280</v>
       </c>
       <c r="B35" t="n">
-        <v>57947</v>
+        <v>56837</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102977</v>
+        <v>206002</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4741,27 +4724,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>O Ölmbrotorp, Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514027</v>
+        <v>514160</v>
       </c>
       <c r="R35" t="n">
-        <v>6584093</v>
+        <v>6583896</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4785,22 +4775,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4815,15 +4805,141 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Per Wedholm</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Per Wedholm</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128848286</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>514154</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6583896</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893048</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893054</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893218</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893056</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926796</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926865</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926927</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926981</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1754,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848252</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1835,6 +1885,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848267</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1961,6 +2016,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848282</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2087,6 +2147,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848289</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2213,6 +2278,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848276</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2332,6 +2402,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131946206</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2447,6 +2522,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926958</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2563,6 +2643,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131843000</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2680,6 +2765,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893046</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2797,6 +2887,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893050</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2919,6 +3014,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893139</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3045,6 +3145,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848257</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3171,6 +3276,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848270</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3297,6 +3407,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848285</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3423,6 +3538,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848292</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3549,6 +3669,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848254</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3675,6 +3800,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848268</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3801,6 +3931,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848283</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3927,6 +4062,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848290</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4053,6 +4193,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848250</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4179,6 +4324,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848265</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4305,6 +4455,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848281</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4431,6 +4586,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848287</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4562,6 +4722,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848264</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4688,6 +4853,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848259</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4814,6 +4984,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848280</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4940,8 +5115,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848286</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>